--- a/outputs/monitor_xlsx/20260128.xlsx
+++ b/outputs/monitor_xlsx/20260128.xlsx
@@ -481,6 +481,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -823,6 +824,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -878,6 +880,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -999,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1107,40 +1110,35 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="V3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1193,12 +1191,7 @@
       <c r="N4" t="n">
         <v>2.71</v>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1236,12 +1229,7 @@
       <c r="M5" t="n">
         <v>-21535</v>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1294,12 +1282,7 @@
       <c r="N6" t="n">
         <v>0.58</v>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1352,12 +1335,7 @@
       <c r="N7" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1410,12 +1388,7 @@
       <c r="N8" t="n">
         <v>4.58</v>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1468,12 +1441,7 @@
       <c r="N9" t="n">
         <v>3.35</v>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1526,12 +1494,7 @@
       <c r="N10" t="n">
         <v>17.27</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1584,12 +1547,7 @@
       <c r="N11" t="n">
         <v>10.72</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1642,12 +1600,7 @@
       <c r="N12" t="n">
         <v>-0.27</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1700,12 +1653,7 @@
       <c r="N13" t="n">
         <v>7.1</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1755,12 +1703,7 @@
       <c r="N14" t="n">
         <v>18.4</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1813,12 +1756,7 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1871,12 +1809,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1926,12 +1859,7 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1984,12 +1912,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2042,12 +1965,7 @@
       <c r="N19" t="n">
         <v>15.29</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2100,11 +2018,6 @@
       <c r="N20" t="n">
         <v>-11.13</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2153,11 +2066,6 @@
       <c r="N21" t="n">
         <v>8.77</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2206,11 +2114,6 @@
       <c r="N22" t="n">
         <v>-8.19</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2259,11 +2162,6 @@
       <c r="N23" t="n">
         <v>-1.04</v>
       </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2312,11 +2210,6 @@
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2364,11 +2257,6 @@
       </c>
       <c r="N25" t="n">
         <v>9.92</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260128.xlsx
+++ b/outputs/monitor_xlsx/20260128.xlsx
@@ -481,7 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -824,7 +823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -880,7 +878,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1002,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1152,44 +1149,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
+          <t>元大台灣50</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>74.2</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>1.57</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" s="7" t="n">
         <v>90901</v>
       </c>
-      <c r="F4" s="7" t="n">
+      <c r="G4" s="7" t="n">
         <v>2680</v>
       </c>
-      <c r="G4" t="n">
-        <v>-56007</v>
-      </c>
       <c r="H4" t="n">
+        <v>3361</v>
+      </c>
+      <c r="I4" t="n">
         <v>284</v>
       </c>
-      <c r="I4" t="n">
-        <v>5582</v>
-      </c>
       <c r="J4" t="n">
+        <v>866</v>
+      </c>
+      <c r="K4" t="n">
         <v>31613</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>6990</v>
       </c>
-      <c r="L4" t="n">
-        <v>37084</v>
-      </c>
       <c r="M4" t="n">
+        <v>36064</v>
+      </c>
+      <c r="N4" t="n">
         <v>-3965508</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.71</v>
+      <c r="O4" t="n">
+        <v>3.53</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1246,41 +1248,46 @@
           <t>華城</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>1040</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>2.46</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" s="6" t="n">
         <v>3300</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>-35</v>
       </c>
-      <c r="G6" t="n">
-        <v>1182</v>
-      </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="I6" t="n">
-        <v>-484</v>
+        <v>-0</v>
       </c>
       <c r="J6" t="n">
+        <v>-588</v>
+      </c>
+      <c r="K6" t="n">
         <v>50</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>2886</v>
       </c>
-      <c r="L6" t="n">
-        <v>14352</v>
-      </c>
       <c r="M6" t="n">
+        <v>14321</v>
+      </c>
+      <c r="N6" t="n">
         <v>-78623</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.58</v>
+      <c r="O6" t="n">
+        <v>10.69</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1352,41 +1359,46 @@
           <t>台達電</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>1280</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" s="7" t="n">
         <v>11623</v>
       </c>
-      <c r="F8" s="7" t="n">
+      <c r="G8" s="7" t="n">
         <v>1175</v>
       </c>
-      <c r="G8" t="n">
-        <v>1590</v>
-      </c>
       <c r="H8" t="n">
+        <v>370</v>
+      </c>
+      <c r="I8" t="n">
         <v>245</v>
       </c>
-      <c r="I8" t="n">
-        <v>1257</v>
-      </c>
       <c r="J8" t="n">
+        <v>1818</v>
+      </c>
+      <c r="K8" t="n">
         <v>185</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>7278</v>
       </c>
-      <c r="L8" t="n">
-        <v>42571</v>
-      </c>
       <c r="M8" t="n">
+        <v>41447</v>
+      </c>
+      <c r="N8" t="n">
         <v>-648554</v>
       </c>
-      <c r="N8" t="n">
-        <v>4.58</v>
+      <c r="O8" t="n">
+        <v>13.01</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1405,41 +1417,46 @@
           <t>台積電</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>1820</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="E9" s="6" t="n">
         <v>2.25</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" s="7" t="n">
         <v>31327</v>
       </c>
-      <c r="F9" s="7" t="n">
+      <c r="G9" s="7" t="n">
         <v>7714</v>
       </c>
-      <c r="G9" t="n">
-        <v>-25600</v>
-      </c>
       <c r="H9" t="n">
+        <v>143</v>
+      </c>
+      <c r="I9" t="n">
         <v>664</v>
       </c>
-      <c r="I9" t="n">
-        <v>-532</v>
-      </c>
       <c r="J9" t="n">
+        <v>3765</v>
+      </c>
+      <c r="K9" t="n">
         <v>402</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>19657</v>
       </c>
-      <c r="L9" t="n">
-        <v>103814</v>
-      </c>
       <c r="M9" t="n">
+        <v>101732</v>
+      </c>
+      <c r="N9" t="n">
         <v>-6482784</v>
       </c>
-      <c r="N9" t="n">
-        <v>3.35</v>
+      <c r="O9" t="n">
+        <v>4.74</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1511,41 +1528,46 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>1900</v>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="E11" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" s="7" t="n">
         <v>4507</v>
       </c>
-      <c r="F11" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>432</v>
       </c>
-      <c r="G11" t="n">
-        <v>4711</v>
-      </c>
       <c r="H11" t="n">
+        <v>4787</v>
+      </c>
+      <c r="I11" t="n">
         <v>-26</v>
       </c>
-      <c r="I11" t="n">
-        <v>-798</v>
-      </c>
       <c r="J11" t="n">
+        <v>-343</v>
+      </c>
+      <c r="K11" t="n">
         <v>242</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1927</v>
       </c>
-      <c r="L11" t="n">
-        <v>10858</v>
-      </c>
       <c r="M11" t="n">
+        <v>10459</v>
+      </c>
+      <c r="N11" t="n">
         <v>-89472</v>
       </c>
-      <c r="N11" t="n">
-        <v>10.72</v>
+      <c r="O11" t="n">
+        <v>14.48</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -1670,38 +1692,46 @@
           <t>光聖</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>1570</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="E14" s="6" t="n">
         <v>9.789999999999999</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" s="7" t="n">
         <v>1578</v>
       </c>
-      <c r="F14" s="7" t="n">
+      <c r="G14" s="7" t="n">
         <v>217</v>
       </c>
-      <c r="G14" t="n">
-        <v>365</v>
+      <c r="H14" t="n">
+        <v>491</v>
       </c>
       <c r="I14" t="n">
-        <v>378</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>297</v>
+      </c>
+      <c r="K14" t="n">
         <v>83</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>5412</v>
       </c>
-      <c r="L14" t="n">
-        <v>25474</v>
-      </c>
       <c r="M14" t="n">
+        <v>25675</v>
+      </c>
+      <c r="N14" t="n">
         <v>-19129</v>
       </c>
-      <c r="N14" t="n">
-        <v>18.4</v>
+      <c r="O14" t="n">
+        <v>17.02</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1720,42 +1750,47 @@
           <t>聯亞</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>-2.44</v>
-      </c>
-      <c r="E15" t="n">
-        <v>905</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>2365</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>2.16</v>
       </c>
       <c r="F15" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G15" s="7" t="n">
         <v>161</v>
       </c>
-      <c r="G15" t="n">
-        <v>-370</v>
-      </c>
       <c r="H15" t="n">
+        <v>-1126</v>
+      </c>
+      <c r="I15" t="n">
         <v>755</v>
       </c>
-      <c r="I15" t="n">
-        <v>1120</v>
-      </c>
       <c r="J15" t="n">
+        <v>1432</v>
+      </c>
+      <c r="K15" t="n">
         <v>-67</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-153</v>
       </c>
-      <c r="L15" t="n">
-        <v>-208</v>
-      </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1876,42 +1911,47 @@
           <t>華星光</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D18" s="7" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="E18" t="n">
-        <v>20497</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>586</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>9.94</v>
       </c>
       <c r="F18" s="7" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G18" s="7" t="n">
         <v>983</v>
       </c>
-      <c r="G18" t="n">
-        <v>-8724</v>
-      </c>
       <c r="H18" t="n">
+        <v>-5142</v>
+      </c>
+      <c r="I18" t="n">
         <v>2668</v>
       </c>
-      <c r="I18" t="n">
-        <v>4350</v>
-      </c>
       <c r="J18" t="n">
+        <v>2918</v>
+      </c>
+      <c r="K18" t="n">
         <v>544</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-2108</v>
       </c>
-      <c r="L18" t="n">
-        <v>-1625</v>
-      </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-2749</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -2126,41 +2166,46 @@
           <t>智邦</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
         <v>1170</v>
       </c>
-      <c r="D23" s="6" t="n">
+      <c r="E23" s="6" t="n">
         <v>1.3</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" s="7" t="n">
         <v>3406</v>
       </c>
-      <c r="F23" s="7" t="n">
+      <c r="G23" s="7" t="n">
         <v>55</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>219</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-354</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-1665</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>74</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2598</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>12984</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>-140169</v>
       </c>
-      <c r="N23" t="n">
-        <v>-1.04</v>
+      <c r="O23" t="n">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="24">
@@ -2174,42 +2219,47 @@
           <t>均華</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>962</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E24" t="n">
-        <v>826</v>
+        <v>1625</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>-6.07</v>
       </c>
       <c r="F24" s="7" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G24" s="7" t="n">
         <v>113</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>131</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>65</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>-29</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>-4</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>208</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2257,6 +2307,218 @@
       </c>
       <c r="N25" t="n">
         <v>9.92</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1035</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>2416</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-526</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-94</v>
+      </c>
+      <c r="I26" t="n">
+        <v>106</v>
+      </c>
+      <c r="J26" t="n">
+        <v>159</v>
+      </c>
+      <c r="K26" t="n">
+        <v>44</v>
+      </c>
+      <c r="L26" t="n">
+        <v>952</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4636</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-106261</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.72</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>4015</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1206</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>-132</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-231</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-144</v>
+      </c>
+      <c r="J27" t="n">
+        <v>8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>58</v>
+      </c>
+      <c r="L27" t="n">
+        <v>409</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1879</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-8868</v>
+      </c>
+      <c r="O27" t="n">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6187</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>321</v>
+      </c>
+      <c r="H28" t="n">
+        <v>594</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>25</v>
+      </c>
+      <c r="L28" t="n">
+        <v>154</v>
+      </c>
+      <c r="M28" t="n">
+        <v>91</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>3096</v>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>-278</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1387</v>
+      </c>
+      <c r="I29" t="n">
+        <v>217</v>
+      </c>
+      <c r="J29" t="n">
+        <v>683</v>
+      </c>
+      <c r="K29" t="n">
+        <v>32</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6418</v>
+      </c>
+      <c r="M29" t="n">
+        <v>32055</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-21466</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.18</v>
       </c>
     </row>
   </sheetData>
